--- a/Scenario Files/HVACScenarios.xlsx
+++ b/Scenario Files/HVACScenarios.xlsx
@@ -554,10 +554,8 @@
       <c r="O2" t="n">
         <v>76</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P2" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -616,10 +614,8 @@
       <c r="O3" t="n">
         <v>71</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="P3" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -678,10 +674,8 @@
       <c r="O4" t="n">
         <v>80</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="P4" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -740,10 +734,8 @@
       <c r="O5" t="n">
         <v>68</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P5" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -802,10 +794,8 @@
       <c r="O6" t="n">
         <v>77</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P6" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -864,10 +854,8 @@
       <c r="O7" t="n">
         <v>81</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P7" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -926,10 +914,8 @@
       <c r="O8" t="n">
         <v>67</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P8" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -988,10 +974,8 @@
       <c r="O9" t="n">
         <v>79</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P9" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -1050,10 +1034,8 @@
       <c r="O10" t="n">
         <v>70</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="P10" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1112,10 +1094,8 @@
       <c r="O11" t="n">
         <v>71</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="P11" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -1174,10 +1154,8 @@
       <c r="O12" t="n">
         <v>79</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P12" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -1236,10 +1214,8 @@
       <c r="O13" t="n">
         <v>69</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P13" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -1298,10 +1274,8 @@
       <c r="O14" t="n">
         <v>79</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P14" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -1360,10 +1334,8 @@
       <c r="O15" t="n">
         <v>76</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P15" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1422,10 +1394,8 @@
       <c r="O16" t="n">
         <v>81</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P16" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -1484,10 +1454,8 @@
       <c r="O17" t="n">
         <v>68</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P17" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -1546,10 +1514,8 @@
       <c r="O18" t="n">
         <v>78</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P18" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -1608,10 +1574,8 @@
       <c r="O19" t="n">
         <v>81</v>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P19" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -1670,10 +1634,8 @@
       <c r="O20" t="n">
         <v>75</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P20" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -1732,10 +1694,8 @@
       <c r="O21" t="n">
         <v>78</v>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P21" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -1794,10 +1754,8 @@
       <c r="O22" t="n">
         <v>69</v>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P22" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -1856,10 +1814,8 @@
       <c r="O23" t="n">
         <v>68</v>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P23" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="24">
@@ -1918,10 +1874,8 @@
       <c r="O24" t="n">
         <v>78</v>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P24" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="25">
@@ -1980,10 +1934,8 @@
       <c r="O25" t="n">
         <v>69</v>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P25" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -2042,10 +1994,8 @@
       <c r="O26" t="n">
         <v>81</v>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P26" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="27">
@@ -2104,10 +2054,8 @@
       <c r="O27" t="n">
         <v>68</v>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P27" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="28">
@@ -2166,10 +2114,8 @@
       <c r="O28" t="n">
         <v>79</v>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P28" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="29">
@@ -2228,10 +2174,8 @@
       <c r="O29" t="n">
         <v>69</v>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P29" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="30">
@@ -2290,10 +2234,8 @@
       <c r="O30" t="n">
         <v>77</v>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P30" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="31">
@@ -2352,10 +2294,8 @@
       <c r="O31" t="n">
         <v>69</v>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P31" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="32">
@@ -2398,7 +2338,7 @@
         <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="L32" t="n">
         <v>8</v>
@@ -2414,10 +2354,8 @@
       <c r="O32" t="n">
         <v>69</v>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P32" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="33">
@@ -2476,10 +2414,8 @@
       <c r="O33" t="n">
         <v>80</v>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P33" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="34">
@@ -2538,10 +2474,8 @@
       <c r="O34" t="n">
         <v>78</v>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P34" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="35">
@@ -2600,10 +2534,8 @@
       <c r="O35" t="n">
         <v>81</v>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="P35" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="36">
@@ -2662,10 +2594,8 @@
       <c r="O36" t="n">
         <v>79</v>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P36" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="37">
@@ -2724,10 +2654,8 @@
       <c r="O37" t="n">
         <v>68</v>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P37" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="38">
@@ -2786,10 +2714,8 @@
       <c r="O38" t="n">
         <v>77</v>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="P38" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="39">
@@ -2848,10 +2774,8 @@
       <c r="O39" t="n">
         <v>76</v>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P39" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="40">
@@ -2910,10 +2834,8 @@
       <c r="O40" t="n">
         <v>72</v>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P40" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="41">
@@ -2972,10 +2894,8 @@
       <c r="O41" t="n">
         <v>80</v>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P41" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="42">
@@ -3034,10 +2954,8 @@
       <c r="O42" t="n">
         <v>65</v>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="P42" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -3096,10 +3014,8 @@
       <c r="O43" t="n">
         <v>81</v>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="P43" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="44">
@@ -3158,16 +3074,14 @@
       <c r="O44" t="n">
         <v>68</v>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P44" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>I'm popping out for a bit, what AC temperature should I set for the single-family?</t>
+          <t>I'm popping out for a bit, what AC temperature should I set for the single-family home?</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3220,10 +3134,8 @@
       <c r="O45" t="n">
         <v>80</v>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P45" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="46">
@@ -3282,10 +3194,8 @@
       <c r="O46" t="n">
         <v>63</v>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="P46" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="47">
@@ -3344,10 +3254,8 @@
       <c r="O47" t="n">
         <v>76</v>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P47" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="48">
@@ -3406,10 +3314,8 @@
       <c r="O48" t="n">
         <v>78</v>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P48" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="49">
@@ -3468,10 +3374,8 @@
       <c r="O49" t="n">
         <v>77</v>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P49" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="50">
@@ -3530,10 +3434,8 @@
       <c r="O50" t="n">
         <v>69</v>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P50" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="51">
@@ -3592,10 +3494,8 @@
       <c r="O51" t="n">
         <v>68</v>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P51" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="52">
@@ -3654,10 +3554,8 @@
       <c r="O52" t="n">
         <v>70</v>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="P52" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="53">
@@ -3716,10 +3614,8 @@
       <c r="O53" t="n">
         <v>76</v>
       </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P53" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="54">
@@ -3778,10 +3674,8 @@
       <c r="O54" t="n">
         <v>76</v>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P54" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="55">
@@ -3840,10 +3734,8 @@
       <c r="O55" t="n">
         <v>77</v>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P55" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="56">
@@ -3902,10 +3794,8 @@
       <c r="O56" t="n">
         <v>68</v>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="P56" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="57">
@@ -3964,10 +3854,8 @@
       <c r="O57" t="n">
         <v>70</v>
       </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="P57" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="58">
@@ -4150,10 +4038,8 @@
       <c r="O60" t="n">
         <v>77</v>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P60" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="61">
@@ -4212,10 +4098,8 @@
       <c r="O61" t="n">
         <v>68</v>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P61" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="62">
@@ -4274,10 +4158,8 @@
       <c r="O62" t="n">
         <v>70</v>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="P62" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="63">
@@ -4336,10 +4218,8 @@
       <c r="O63" t="n">
         <v>70</v>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="P63" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="64">
@@ -4398,10 +4278,8 @@
       <c r="O64" t="n">
         <v>69</v>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="P64" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="65">
@@ -4460,10 +4338,8 @@
       <c r="O65" t="n">
         <v>77</v>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P65" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="66">
@@ -4522,10 +4398,8 @@
       <c r="O66" t="n">
         <v>68</v>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P66" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="67">
@@ -4584,10 +4458,8 @@
       <c r="O67" t="n">
         <v>75</v>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P67" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -4646,10 +4518,8 @@
       <c r="O68" t="n">
         <v>68</v>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="P68" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="69">
@@ -4708,10 +4578,8 @@
       <c r="O69" t="n">
         <v>78</v>
       </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P69" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="70">
@@ -4770,10 +4638,8 @@
       <c r="O70" t="n">
         <v>70</v>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P70" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="71">
@@ -4832,10 +4698,8 @@
       <c r="O71" t="n">
         <v>69</v>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P71" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="72">
@@ -4894,10 +4758,8 @@
       <c r="O72" t="n">
         <v>66</v>
       </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="P72" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="73">
@@ -4956,10 +4818,8 @@
       <c r="O73" t="n">
         <v>68</v>
       </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="P73" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="74">
@@ -5018,10 +4878,8 @@
       <c r="O74" t="n">
         <v>66</v>
       </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="P74" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="75">
@@ -5080,10 +4938,8 @@
       <c r="O75" t="n">
         <v>68</v>
       </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P75" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="76">
@@ -5142,10 +4998,8 @@
       <c r="O76" t="n">
         <v>72</v>
       </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="P76" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="77">
@@ -5204,10 +5058,8 @@
       <c r="O77" t="n">
         <v>72</v>
       </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="P77" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="78">
@@ -5266,10 +5118,8 @@
       <c r="O78" t="n">
         <v>68</v>
       </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P78" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="79">
@@ -5328,10 +5178,8 @@
       <c r="O79" t="n">
         <v>72</v>
       </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="P79" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="80">
@@ -5390,10 +5238,8 @@
       <c r="O80" t="n">
         <v>76</v>
       </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P80" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="81">
@@ -5452,10 +5298,8 @@
       <c r="O81" t="n">
         <v>80</v>
       </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="P81" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="82">
@@ -5514,10 +5358,8 @@
       <c r="O82" t="n">
         <v>77</v>
       </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P82" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="83">
@@ -5576,10 +5418,8 @@
       <c r="O83" t="n">
         <v>81</v>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P83" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="84">
@@ -5638,10 +5478,8 @@
       <c r="O84" t="n">
         <v>76</v>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="P84" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="85">
@@ -5700,10 +5538,8 @@
       <c r="O85" t="n">
         <v>81</v>
       </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P85" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="86">
@@ -5762,16 +5598,14 @@
       <c r="O86" t="n">
         <v>77</v>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="P86" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family?</t>
+          <t>I'm heading out for a quick errand, what heat temperature should I set for the single-family home?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5824,10 +5658,8 @@
       <c r="O87" t="n">
         <v>66</v>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="P87" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="88">
@@ -5886,10 +5718,8 @@
       <c r="O88" t="n">
         <v>69</v>
       </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="P88" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="89">
@@ -5948,10 +5778,8 @@
       <c r="O89" t="n">
         <v>63</v>
       </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="P89" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="90">
@@ -6010,10 +5838,8 @@
       <c r="O90" t="n">
         <v>76</v>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P90" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="91">
@@ -6072,10 +5898,8 @@
       <c r="O91" t="n">
         <v>63</v>
       </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="P91" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="92">
@@ -6134,10 +5958,8 @@
       <c r="O92" t="n">
         <v>79</v>
       </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="P92" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="93">
@@ -6196,10 +6018,8 @@
       <c r="O93" t="n">
         <v>67</v>
       </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P93" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="94">
@@ -6258,10 +6078,8 @@
       <c r="O94" t="n">
         <v>65</v>
       </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="P94" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="95">
@@ -6320,10 +6138,8 @@
       <c r="O95" t="n">
         <v>61</v>
       </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="P95" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="96">
@@ -6382,10 +6198,8 @@
       <c r="O96" t="n">
         <v>67</v>
       </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="P96" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="97">
@@ -6444,10 +6258,8 @@
       <c r="O97" t="n">
         <v>63</v>
       </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="P97" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="98">
@@ -6506,10 +6318,8 @@
       <c r="O98" t="n">
         <v>65</v>
       </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="P98" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="99">
@@ -6568,10 +6378,8 @@
       <c r="O99" t="n">
         <v>63</v>
       </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="P99" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="100">
@@ -6630,10 +6438,8 @@
       <c r="O100" t="n">
         <v>65</v>
       </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="P100" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="101">
@@ -6692,10 +6498,8 @@
       <c r="O101" t="n">
         <v>76</v>
       </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="P101" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="102">
@@ -6754,10 +6558,8 @@
       <c r="O102" t="n">
         <v>81</v>
       </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="P102" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="103">
@@ -6816,10 +6618,8 @@
       <c r="O103" t="n">
         <v>64</v>
       </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="P103" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="104">
@@ -6878,10 +6678,8 @@
       <c r="O104" t="n">
         <v>75</v>
       </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="P104" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="105">
